--- a/Result/profitability/3213.xlsx
+++ b/Result/profitability/3213.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM74"/>
+  <dimension ref="A1:AM75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,16 +669,16 @@
         <v>1.52</v>
       </c>
       <c r="M2" t="n">
-        <v>1.79625</v>
+        <v>2.02625</v>
       </c>
       <c r="N2" t="n">
-        <v>30.36625</v>
+        <v>31.75125</v>
       </c>
       <c r="O2" t="n">
         <v>0</v>
       </c>
       <c r="P2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q2" t="n">
         <v>0</v>
@@ -780,10 +780,10 @@
         <v>1.39</v>
       </c>
       <c r="M3" t="n">
-        <v>1.8225</v>
+        <v>1.98875</v>
       </c>
       <c r="N3" t="n">
-        <v>30.5475</v>
+        <v>30.88625</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
@@ -899,10 +899,10 @@
         <v>1.67</v>
       </c>
       <c r="M4" t="n">
-        <v>1.82</v>
+        <v>1.84375</v>
       </c>
       <c r="N4" t="n">
-        <v>29.52125</v>
+        <v>29.325</v>
       </c>
       <c r="O4" t="n">
         <v>1</v>
@@ -1018,10 +1018,10 @@
         <v>1.85</v>
       </c>
       <c r="M5" t="n">
-        <v>1.6975</v>
+        <v>2.00125</v>
       </c>
       <c r="N5" t="n">
-        <v>28.8625</v>
+        <v>29.4875</v>
       </c>
       <c r="O5" t="n">
         <v>1</v>
@@ -1137,16 +1137,16 @@
         <v>1.7</v>
       </c>
       <c r="M6" t="n">
-        <v>1.83625</v>
+        <v>1.88125</v>
       </c>
       <c r="N6" t="n">
-        <v>28.2975</v>
+        <v>29.3475</v>
       </c>
       <c r="O6" t="n">
         <v>1</v>
       </c>
       <c r="P6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q6" t="n">
         <v>0</v>
@@ -1155,7 +1155,7 @@
         <v>0</v>
       </c>
       <c r="S6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T6" t="n">
         <v>0</v>
@@ -1264,10 +1264,10 @@
         <v>2.05</v>
       </c>
       <c r="M7" t="n">
-        <v>1.76</v>
+        <v>1.97375</v>
       </c>
       <c r="N7" t="n">
-        <v>28.9675</v>
+        <v>30.2725</v>
       </c>
       <c r="O7" t="n">
         <v>1</v>
@@ -1391,10 +1391,10 @@
         <v>1.76</v>
       </c>
       <c r="M8" t="n">
-        <v>1.81625</v>
+        <v>1.87</v>
       </c>
       <c r="N8" t="n">
-        <v>28.9025</v>
+        <v>28.8775</v>
       </c>
       <c r="O8" t="n">
         <v>1</v>
@@ -9826,6 +9826,133 @@
       </c>
       <c r="AM74" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>3213</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>1008</v>
+      </c>
+      <c r="D75" t="n">
+        <v>647</v>
+      </c>
+      <c r="E75" t="n">
+        <v>361</v>
+      </c>
+      <c r="F75" t="n">
+        <v>35.77</v>
+      </c>
+      <c r="G75" t="n">
+        <v>267</v>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>26.47%</t>
+        </is>
+      </c>
+      <c r="I75" t="n">
+        <v>8</v>
+      </c>
+      <c r="J75" t="n">
+        <v>275</v>
+      </c>
+      <c r="K75" t="n">
+        <v>177</v>
+      </c>
+      <c r="L75" t="n">
+        <v>3.02</v>
+      </c>
+      <c r="M75" t="n">
+        <v>1.98375</v>
+      </c>
+      <c r="N75" t="n">
+        <v>31.2875</v>
+      </c>
+      <c r="O75" t="n">
+        <v>1</v>
+      </c>
+      <c r="P75" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>1</v>
+      </c>
+      <c r="R75" t="n">
+        <v>0</v>
+      </c>
+      <c r="S75" t="n">
+        <v>1</v>
+      </c>
+      <c r="T75" t="n">
+        <v>0</v>
+      </c>
+      <c r="U75" t="n">
+        <v>1</v>
+      </c>
+      <c r="V75" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W75" t="n">
+        <v>0.4300000000000002</v>
+      </c>
+      <c r="X75" t="n">
+        <v>0.1660231660231661</v>
+      </c>
+      <c r="Y75" t="n">
+        <v>-0.1999999999999957</v>
+      </c>
+      <c r="Z75" t="n">
+        <v>-0.005560189046427411</v>
+      </c>
+      <c r="AA75" t="n">
+        <v>2.43</v>
+      </c>
+      <c r="AB75" t="n">
+        <v>4.118644067796611</v>
+      </c>
+      <c r="AC75" t="n">
+        <v>5.000000000000004</v>
+      </c>
+      <c r="AD75" t="n">
+        <v>0.16249593760156</v>
+      </c>
+      <c r="AE75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>EPS成長 / 毛利率成長</t>
+        </is>
+      </c>
+      <c r="AK75" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL75" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM75" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
